--- a/templates/office/EMP_EXE_020_AI프롬프트명세서.xlsx
+++ b/templates/office/EMP_EXE_020_AI프롬프트명세서.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 AI 기반 화장품 표시광고 심의 및 리스크 예방 시스템 구축</t>
+          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>(주)아모레퍼시픽 (HANBIT GLOBAL)</t>
+          <t>㈜한빛글로벌 (Hanbit Global Corp.)</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>㈜그로브소프트 (EMPASY)</t>
+          <t>㈜엠파시 (Empasy Inc.)</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>위반된 금지 표현을 화장품법 허용 범위 내의 안전하고 세련된 마케팅 문구로 변환</t>
+          <t>위반된 금지 표현을 표시·광고 공정화법 허용 범위 내의 안전하고 세련된 마케팅 문구로 변환</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>설화수, 헤라 등 브랜드별 지정 키워드 및 지양 표현 준수 여부 평가</t>
+          <t>루미에르, 벨르코어 등 브랜드별 지정 키워드 및 지양 표현 준수 여부 평가</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">

--- a/templates/office/EMP_EXE_020_AI프롬프트명세서.xlsx
+++ b/templates/office/EMP_EXE_020_AI프롬프트명세서.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SyncGuard AI 모델 파이프라인별 LLM 프롬프트 템플릿 및 입출력 스키마 명세</t>
+          <t>SyncFlow AI 모델 파이프라인별 LLM 프롬프트 템플릿 및 입출력 스키마 명세</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
+          <t>한빛글로벌 지능형 공급망 구매·조달 계약 및 부품 품질규격 AI 검증 플랫폼(SyncFlow AI) 구축</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>15건 (OCR 정제, 룰 매핑, 법령 추론, 대체문구 추천 등)</t>
+          <t>15건 (OCR 정제, 룰 매핑, 법령 추론, 표준수정조항 추천 등)</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
     <row r="2">
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>AI 심의 파이프라인 프롬프트 명세 목록 (15 Prompts)</t>
+          <t>AI 검증 파이프라인 프롬프트 명세 목록 (15 Prompts)</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>시안 이미지 텍스트 정제 및 문장 분할</t>
+          <t>계약·도서 이미지 텍스트 정제 및 문장 분할</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>시안 이미지에서 줄바꿈된 카피를 자연스러운 단일 문장으로 결합하고 각주(*)를 분리 태깅</t>
+          <t>계약·도서 이미지에서 줄바꿈된 조항를 자연스러운 단일 문장으로 결합하고 특약주석(*)를 분리 태깅</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>금지어/주의어 키워드 매칭 및 컨텍스트 판정</t>
+          <t>독소조항/보완조항 키워드 매칭 및 컨텍스트 판정</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>추출된 문장에서 100대 금지어 사전을 대조하여 실제 위반 문맥인지 판단</t>
+          <t>추출된 문장에서 100대 독소조항 사전을 대조하여 실제 위반 문맥인지 판단</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>의약품 오인 판정</t>
+          <t>불공정 독소조항 판정</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>의약품 효능 표방 및 신체 영향 심층 분석</t>
+          <t>불공정특약 성능규격 표방 및 신체 영향 심층 분석</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>질병 치료, 세포 재생, 진피 침투 등 의약품 오인 소지를 식약처 고시 기준으로 판정</t>
+          <t>일방 면책, 무한 손해배상, 일방 단가인하 등 불공정 독소조항 소지를 공정위·표준원 고시 기준으로 판정</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>문장 텍스트 + 식약처 RAG 청크</t>
+          <t>문장 텍스트 + 공정위·표준원 RAG 청크</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>기능성 오인 판정</t>
+          <t>핵심규격 오인 판정</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>미보고 기능성 효능 표방 여부 판정</t>
+          <t>미보고 핵심규격 성능규격 표방 여부 판정</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>미백/주름/자외선 등 기능성 화장품 허가 보고 없이 효능을 암시했는지 판정</t>
+          <t>절연성/내진동/전자파 등 핵심규격 전장부품 허가 보고 없이 성능규격을 암시했는지 판정</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>최상급/절대적 수치 표현 실증 요건 검토</t>
+          <t>최상급/절대적 수치 표현 시험검증 요건 검토</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>100%, 최초, 최고 등 절대적 표현에 대해 요구되는 실증 증빙 요건 도출</t>
+          <t>100%, 최초, 최고 등 절대적 표현에 대해 요구되는 시험검증 증빙 요건 도출</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>문장 텍스트 + 실증 요건 룰셋</t>
+          <t>문장 텍스트 + 시험검증 요건 룰셋</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>대체 문구 생성</t>
+          <t>대체 조항 생성</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>합법적 권장 대체 문구 2개 자동 생성</t>
+          <t>합법적 권장 대체 조항 2개 자동 생성</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>위반된 금지 표현을 표시·광고 공정화법 허용 범위 내의 안전하고 세련된 마케팅 문구로 변환</t>
+          <t>위반된 금지 표현을 하도급거래 공정화법 허용 범위 내의 안전하고 세련된 구매조달 조항으로 변환</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>위반 문장 + 위반 사유 + 브랜드명</t>
+          <t>위반 문장 + 위반 사유 + 사업본부명</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>브랜드 톤앤매너</t>
+          <t>사업본부 톤앤매너</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>브랜드 고유 표현 적합성 검증</t>
+          <t>사업본부 고유 표현 적합성 검증</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>루미에르, 벨르코어 등 브랜드별 지정 키워드 및 지양 표현 준수 여부 평가</t>
+          <t>전장시스템, 배터리모듈 등 사업부별 지정 키워드 및 지양 표현 준수 여부 평가</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>문장 텍스트 + 브랜드 가이드라인</t>
+          <t>문장 텍스트 + 사업본부 가이드라인</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>성분 효능 검증</t>
+          <t>성분 성능규격 검증</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>원료 효능 표방 시 각주 충족성 검증</t>
+          <t>원소재 성능규격 표방 시 특약주석 충족성 검증</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>특정 성분(레티놀 등)의 효능 설명 시 '원료적 특성에 한함' 각주 누락 여부 검토</t>
+          <t>특정 성분(육가크롬 등)의 성능규격 설명 시 '원소재적 특성에 한함' 특약주석 누락 여부 검토</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>소구 문장 + 각주 리스트</t>
+          <t>기술사양 조항 + 특약주석 리스트</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>소구 수치와 인체적용시험 보고서 1:1 매치</t>
+          <t>기술사양 수치와 공인신뢰성시험 보고서 1:1 매치</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>시안에 기재된 수치(탄력 24% 등)와 보유 시험성적서 결과 수치 대조</t>
+          <t>계약·도서에 기재된 수치(인장강도 24% 등)와 보유 시험성적서 결과 수치 대조</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>소구 수치 + 성적서 메타</t>
+          <t>기술사양 수치 + 성적서 메타</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>법정 각주 생성</t>
+          <t>품질보증 주석 생성</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>식약처 필수 표기 각주 자동 텍스트 렌더링</t>
+          <t>공정위·표준원 필수 표기 특약주석 자동 텍스트 렌더링</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>시험기관, 시험기간, 피험자 수, 대상 부위를 식약처 표준 각주 문장으로 생성</t>
+          <t>시험기관, 시험기간, 시험시료 수, 대상 부위를 공정위·표준원 표준 특약주석 문장으로 생성</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>텍스트 (각주 표준 문장)</t>
+          <t>텍스트 (특약주석 표준 문장)</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>RA 심의관용 3줄 종합 심의 의견 생성</t>
+          <t>법무·QA 검토위원용 3줄 종합 검증 의견 생성</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>전체 슬라이드의 위반 항목을 취합하여 마케터가 수정할 핵심 3대 개선점 요약</t>
+          <t>전체 슬라이드의 위반 항목을 취합하여 구매담당자가 수정할 핵심 3대 개선점 요약</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>재심의 변경점 분석</t>
+          <t>재검증 변경점 분석</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>시안 수정본과 초안 간 Diff 분석</t>
+          <t>계약·도서 수정본과 초안 간 Diff 분석</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>반려 후 재신청된 시안에서 지적 사항이 올바르게 수정되었는지 변경점 추출</t>
+          <t>반려 후 재신청된 계약·도서에서 지적 사항이 올바르게 수정되었는지 변경점 추출</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>미국 FDA OTC, 중국 NMPA 화장품 규정 기준 위반 소지 검출</t>
+          <t>미국 IATF OTC, 중국 RoHS 전장부품 규정 기준 위반 소지 검출</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>SNS 숏폼 광고 비속어 및 저속 표현 차단</t>
+          <t>SNS 도면요약 구매계약 비속어 및 저속 표현 차단</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>MZ 타겟 숏폼 시안의 부적절한 유행어, 비속어, 성적 수치심 유발 단어 검출</t>
+          <t>MZ 타겟 도면요약 계약·도서의 부적절한 유행어, 비속어, 성적 수치심 유발 단어 검출</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>식약처 민원 소명용 합법성 입증 논리 작성</t>
+          <t>공정위·표준원 민원 소명용 합법성 입증 논리 작성</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>문제 문구 + 시험성적서 + 법령</t>
+          <t>문제 조항 + 시험성적서 + 법령</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
